--- a/2026_DSAIML_Club_Batch/Attendance.xlsx
+++ b/2026_DSAIML_Club_Batch/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\all_batches\2026_DSAIML_Club_Batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B5D03E-1A38-43FC-9E71-077380063F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E9D190-6565-4FD7-B06A-B50B7EF66128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="25">
   <si>
     <t>Ahmedabad</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>Deep Raval</t>
+  </si>
+  <si>
+    <t>Shalin Patel</t>
   </si>
 </sst>
 </file>
@@ -421,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -429,7 +432,7 @@
     <col min="3" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -490,8 +493,17 @@
       <c r="T1" s="2">
         <v>46078</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U1" s="2">
+        <v>46079</v>
+      </c>
+      <c r="V1" s="2">
+        <v>46084</v>
+      </c>
+      <c r="W1" s="2">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -552,8 +564,11 @@
       <c r="T2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -614,8 +629,11 @@
       <c r="T3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -676,8 +694,11 @@
       <c r="T4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -738,8 +759,11 @@
       <c r="T5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -800,8 +824,11 @@
       <c r="T6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -862,8 +889,11 @@
       <c r="T7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -924,8 +954,11 @@
       <c r="T8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -987,7 +1020,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1048,8 +1081,17 @@
       <c r="T10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U10" t="s">
+        <v>17</v>
+      </c>
+      <c r="V10" t="s">
+        <v>17</v>
+      </c>
+      <c r="W10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1110,8 +1152,11 @@
       <c r="T11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1172,8 +1217,11 @@
       <c r="T12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1234,8 +1282,11 @@
       <c r="T13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1296,8 +1347,11 @@
       <c r="T14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1358,8 +1412,11 @@
       <c r="T15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1420,8 +1477,11 @@
       <c r="T16" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1481,6 +1541,20 @@
       </c>
       <c r="T17" t="s">
         <v>16</v>
+      </c>
+      <c r="W17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>0</v>
+      </c>
+      <c r="W18" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/2026_DSAIML_Club_Batch/Attendance.xlsx
+++ b/2026_DSAIML_Club_Batch/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\all_batches\2026_DSAIML_Club_Batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E9D190-6565-4FD7-B06A-B50B7EF66128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CC22DF-845F-4339-834C-7215E0F4EA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="26">
   <si>
     <t>Ahmedabad</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>Shalin Patel</t>
+  </si>
+  <si>
+    <t>Raghav Thakkar</t>
   </si>
 </sst>
 </file>
@@ -424,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -432,7 +435,7 @@
     <col min="3" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -502,8 +505,20 @@
       <c r="W1" s="2">
         <v>46086</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X1" s="2">
+        <v>46118</v>
+      </c>
+      <c r="Y1" s="2">
+        <v>46091</v>
+      </c>
+      <c r="Z1" s="2">
+        <v>46092</v>
+      </c>
+      <c r="AA1" s="2">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -567,8 +582,17 @@
       <c r="W2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -632,8 +656,20 @@
       <c r="W3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -697,8 +733,17 @@
       <c r="W4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y4" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -762,8 +807,17 @@
       <c r="W5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -827,8 +881,17 @@
       <c r="W6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -892,8 +955,17 @@
       <c r="W7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -957,8 +1029,17 @@
       <c r="W8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1019,8 +1100,17 @@
       <c r="T9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1090,8 +1180,17 @@
       <c r="W10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y10" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1155,8 +1254,17 @@
       <c r="W11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y11" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1220,8 +1328,17 @@
       <c r="W12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y12" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1285,8 +1402,17 @@
       <c r="W13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y13" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1350,8 +1476,20 @@
       <c r="W14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X14" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1415,8 +1553,17 @@
       <c r="W15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y15" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1480,8 +1627,17 @@
       <c r="W16" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y16" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1545,8 +1701,17 @@
       <c r="W17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y17" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1554,6 +1719,38 @@
         <v>0</v>
       </c>
       <c r="W18" t="s">
+        <v>18</v>
+      </c>
+      <c r="X18" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>0</v>
+      </c>
+      <c r="X19" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA19" t="s">
         <v>18</v>
       </c>
     </row>

--- a/2026_DSAIML_Club_Batch/Attendance.xlsx
+++ b/2026_DSAIML_Club_Batch/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\all_batches\2026_DSAIML_Club_Batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CC22DF-845F-4339-834C-7215E0F4EA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC2E7EE-0A4E-4BF0-99E2-44A6BF6A3962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="26">
   <si>
     <t>Ahmedabad</t>
   </si>
@@ -427,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -435,7 +435,7 @@
     <col min="3" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -517,8 +517,17 @@
       <c r="AA1" s="2">
         <v>46093</v>
       </c>
+      <c r="AB1" s="2">
+        <v>46098</v>
+      </c>
+      <c r="AC1" s="2">
+        <v>46099</v>
+      </c>
+      <c r="AD1" s="2">
+        <v>46100</v>
+      </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -591,8 +600,17 @@
       <c r="AA2" t="s">
         <v>17</v>
       </c>
+      <c r="AB2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -668,8 +686,17 @@
       <c r="AA3" t="s">
         <v>16</v>
       </c>
+      <c r="AB3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -742,8 +769,17 @@
       <c r="AA4" t="s">
         <v>16</v>
       </c>
+      <c r="AB4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -816,8 +852,17 @@
       <c r="AA5" t="s">
         <v>18</v>
       </c>
+      <c r="AB5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -890,8 +935,17 @@
       <c r="AA6" t="s">
         <v>16</v>
       </c>
+      <c r="AB6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -964,8 +1018,17 @@
       <c r="AA7" t="s">
         <v>16</v>
       </c>
+      <c r="AB7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1038,8 +1101,17 @@
       <c r="AA8" t="s">
         <v>18</v>
       </c>
+      <c r="AB8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1109,8 +1181,17 @@
       <c r="AA9" t="s">
         <v>17</v>
       </c>
+      <c r="AB9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1189,8 +1270,17 @@
       <c r="AA10" t="s">
         <v>16</v>
       </c>
+      <c r="AB10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1263,8 +1353,17 @@
       <c r="AA11" t="s">
         <v>17</v>
       </c>
+      <c r="AB11" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1337,8 +1436,17 @@
       <c r="AA12" t="s">
         <v>18</v>
       </c>
+      <c r="AB12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1411,8 +1519,17 @@
       <c r="AA13" t="s">
         <v>17</v>
       </c>
+      <c r="AB13" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1488,8 +1605,17 @@
       <c r="AA14" t="s">
         <v>16</v>
       </c>
+      <c r="AB14" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1562,8 +1688,17 @@
       <c r="AA15" t="s">
         <v>16</v>
       </c>
+      <c r="AB15" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1636,8 +1771,17 @@
       <c r="AA16" t="s">
         <v>17</v>
       </c>
+      <c r="AB16" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1710,8 +1854,17 @@
       <c r="AA17" t="s">
         <v>16</v>
       </c>
+      <c r="AB17" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1733,8 +1886,17 @@
       <c r="AA18" t="s">
         <v>16</v>
       </c>
+      <c r="AB18" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1751,6 +1913,15 @@
         <v>18</v>
       </c>
       <c r="AA19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD19" t="s">
         <v>18</v>
       </c>
     </row>

--- a/2026_DSAIML_Club_Batch/Attendance.xlsx
+++ b/2026_DSAIML_Club_Batch/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\all_batches\2026_DSAIML_Club_Batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC2E7EE-0A4E-4BF0-99E2-44A6BF6A3962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9330991-E0E4-4E76-8C2B-9CC621B501AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="26">
   <si>
     <t>Ahmedabad</t>
   </si>
@@ -427,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -435,7 +435,7 @@
     <col min="3" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -526,8 +526,11 @@
       <c r="AD1" s="2">
         <v>46100</v>
       </c>
+      <c r="AE1" s="2">
+        <v>46107</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -609,8 +612,11 @@
       <c r="AD2" t="s">
         <v>16</v>
       </c>
+      <c r="AE2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -695,8 +701,11 @@
       <c r="AD3" t="s">
         <v>18</v>
       </c>
+      <c r="AE3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -778,8 +787,11 @@
       <c r="AD4" t="s">
         <v>16</v>
       </c>
+      <c r="AE4" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -861,8 +873,11 @@
       <c r="AD5" t="s">
         <v>18</v>
       </c>
+      <c r="AE5" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -944,8 +959,11 @@
       <c r="AD6" t="s">
         <v>17</v>
       </c>
+      <c r="AE6" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1027,8 +1045,11 @@
       <c r="AD7" t="s">
         <v>16</v>
       </c>
+      <c r="AE7" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1110,8 +1131,11 @@
       <c r="AD8" t="s">
         <v>18</v>
       </c>
+      <c r="AE8" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1190,8 +1214,11 @@
       <c r="AD9" t="s">
         <v>17</v>
       </c>
+      <c r="AE9" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1279,8 +1306,11 @@
       <c r="AD10" t="s">
         <v>17</v>
       </c>
+      <c r="AE10" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1362,8 +1392,11 @@
       <c r="AD11" t="s">
         <v>16</v>
       </c>
+      <c r="AE11" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1445,8 +1478,11 @@
       <c r="AD12" t="s">
         <v>18</v>
       </c>
+      <c r="AE12" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1528,8 +1564,11 @@
       <c r="AD13" t="s">
         <v>17</v>
       </c>
+      <c r="AE13" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1614,8 +1653,11 @@
       <c r="AD14" t="s">
         <v>16</v>
       </c>
+      <c r="AE14" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1697,8 +1739,11 @@
       <c r="AD15" t="s">
         <v>16</v>
       </c>
+      <c r="AE15" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1780,8 +1825,11 @@
       <c r="AD16" t="s">
         <v>16</v>
       </c>
+      <c r="AE16" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1863,8 +1911,11 @@
       <c r="AD17" t="s">
         <v>18</v>
       </c>
+      <c r="AE17" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1895,8 +1946,11 @@
       <c r="AD18" t="s">
         <v>16</v>
       </c>
+      <c r="AE18" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1923,6 +1977,9 @@
       </c>
       <c r="AD19" t="s">
         <v>18</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
